--- a/excel/Завод 1/t2.xlsx
+++ b/excel/Завод 1/t2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/72c13503b0c010a4/Desktop/Прект_10/.venv/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/72c13503b0c010a4/Desktop/Прект_10/excel/Завод 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_AD4DF75460589B3ACB728430E75B765A5BDEDD91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83D038DC-022A-4C12-A5AE-1FC1958D6B19}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_AD4DF75460589B3ACB728430E75B765A5BDEDD91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8912F5-0A79-4738-8114-EAC5C597670C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6380" yWindow="4030" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -659,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="14">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1127,7 +1127,7 @@
         <v>2049</v>
       </c>
       <c r="B21" s="9">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C21" s="9">
         <v>0</v>
@@ -1165,7 +1165,1157 @@
         <v>0</v>
       </c>
       <c r="G22" s="17">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="13">
+        <v>2051</v>
+      </c>
+      <c r="B23" s="9">
+        <v>185</v>
+      </c>
+      <c r="C23" s="16">
+        <v>0</v>
+      </c>
+      <c r="D23" s="16">
+        <v>15</v>
+      </c>
+      <c r="E23" s="16">
+        <v>15</v>
+      </c>
+      <c r="F23" s="16">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="13">
+        <v>2052</v>
+      </c>
+      <c r="B24" s="9">
+        <v>190</v>
+      </c>
+      <c r="C24" s="16">
+        <v>0</v>
+      </c>
+      <c r="D24" s="16">
+        <v>15</v>
+      </c>
+      <c r="E24" s="16">
+        <v>10</v>
+      </c>
+      <c r="F24" s="16">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="13">
+        <v>2053</v>
+      </c>
+      <c r="B25" s="16">
+        <v>195</v>
+      </c>
+      <c r="C25" s="16">
+        <v>0</v>
+      </c>
+      <c r="D25" s="16">
+        <v>15</v>
+      </c>
+      <c r="E25" s="16">
+        <v>15</v>
+      </c>
+      <c r="F25" s="16">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
         <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="15">
+        <v>2054</v>
+      </c>
+      <c r="B26" s="9">
+        <v>200</v>
+      </c>
+      <c r="C26" s="16">
+        <v>0</v>
+      </c>
+      <c r="D26" s="16">
+        <v>15</v>
+      </c>
+      <c r="E26" s="16">
+        <v>15</v>
+      </c>
+      <c r="F26" s="16">
+        <v>0</v>
+      </c>
+      <c r="G26" s="17">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="13">
+        <v>2055</v>
+      </c>
+      <c r="B27" s="9">
+        <v>205</v>
+      </c>
+      <c r="C27" s="16">
+        <v>0</v>
+      </c>
+      <c r="D27" s="16">
+        <v>10</v>
+      </c>
+      <c r="E27" s="16">
+        <v>15</v>
+      </c>
+      <c r="F27" s="16">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="13">
+        <v>2056</v>
+      </c>
+      <c r="B28" s="16">
+        <v>210</v>
+      </c>
+      <c r="C28" s="16">
+        <v>0</v>
+      </c>
+      <c r="D28" s="16">
+        <v>15</v>
+      </c>
+      <c r="E28" s="16">
+        <v>15</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="13">
+        <v>2057</v>
+      </c>
+      <c r="B29" s="9">
+        <v>215</v>
+      </c>
+      <c r="C29" s="16">
+        <v>0</v>
+      </c>
+      <c r="D29" s="16">
+        <v>15</v>
+      </c>
+      <c r="E29" s="16">
+        <v>15</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="15">
+        <v>2058</v>
+      </c>
+      <c r="B30" s="9">
+        <v>220</v>
+      </c>
+      <c r="C30" s="16">
+        <v>0</v>
+      </c>
+      <c r="D30" s="16">
+        <v>15</v>
+      </c>
+      <c r="E30" s="16">
+        <v>15</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0</v>
+      </c>
+      <c r="G30" s="17">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="13">
+        <v>2059</v>
+      </c>
+      <c r="B31" s="16">
+        <v>225</v>
+      </c>
+      <c r="C31" s="16">
+        <v>0</v>
+      </c>
+      <c r="D31" s="16">
+        <v>15</v>
+      </c>
+      <c r="E31" s="16">
+        <v>15</v>
+      </c>
+      <c r="F31" s="16">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="13">
+        <v>2060</v>
+      </c>
+      <c r="B32" s="9">
+        <v>230</v>
+      </c>
+      <c r="C32" s="16">
+        <v>0</v>
+      </c>
+      <c r="D32" s="16">
+        <v>15</v>
+      </c>
+      <c r="E32" s="16">
+        <v>10</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="13">
+        <v>2061</v>
+      </c>
+      <c r="B33" s="9">
+        <v>235</v>
+      </c>
+      <c r="C33" s="16">
+        <v>0</v>
+      </c>
+      <c r="D33" s="16">
+        <v>15</v>
+      </c>
+      <c r="E33" s="16">
+        <v>15</v>
+      </c>
+      <c r="F33" s="16">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="15">
+        <v>2062</v>
+      </c>
+      <c r="B34" s="16">
+        <v>240</v>
+      </c>
+      <c r="C34" s="16">
+        <v>0</v>
+      </c>
+      <c r="D34" s="16">
+        <v>15</v>
+      </c>
+      <c r="E34" s="16">
+        <v>15</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0</v>
+      </c>
+      <c r="G34" s="17">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="13">
+        <v>2063</v>
+      </c>
+      <c r="B35" s="9">
+        <v>245</v>
+      </c>
+      <c r="C35" s="16">
+        <v>0</v>
+      </c>
+      <c r="D35" s="16">
+        <v>10</v>
+      </c>
+      <c r="E35" s="16">
+        <v>15</v>
+      </c>
+      <c r="F35" s="16">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="13">
+        <v>2064</v>
+      </c>
+      <c r="B36" s="9">
+        <v>250</v>
+      </c>
+      <c r="C36" s="16">
+        <v>0</v>
+      </c>
+      <c r="D36" s="16">
+        <v>15</v>
+      </c>
+      <c r="E36" s="16">
+        <v>15</v>
+      </c>
+      <c r="F36" s="16">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="13">
+        <v>2065</v>
+      </c>
+      <c r="B37" s="16">
+        <v>255</v>
+      </c>
+      <c r="C37" s="16">
+        <v>0</v>
+      </c>
+      <c r="D37" s="16">
+        <v>15</v>
+      </c>
+      <c r="E37" s="16">
+        <v>15</v>
+      </c>
+      <c r="F37" s="16">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="15">
+        <v>2066</v>
+      </c>
+      <c r="B38" s="9">
+        <v>260</v>
+      </c>
+      <c r="C38" s="16">
+        <v>0</v>
+      </c>
+      <c r="D38" s="16">
+        <v>15</v>
+      </c>
+      <c r="E38" s="16">
+        <v>15</v>
+      </c>
+      <c r="F38" s="16">
+        <v>0</v>
+      </c>
+      <c r="G38" s="17">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="13">
+        <v>2067</v>
+      </c>
+      <c r="B39" s="9">
+        <v>265</v>
+      </c>
+      <c r="C39" s="16">
+        <v>0</v>
+      </c>
+      <c r="D39" s="16">
+        <v>15</v>
+      </c>
+      <c r="E39" s="16">
+        <v>15</v>
+      </c>
+      <c r="F39" s="16">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="13">
+        <v>2068</v>
+      </c>
+      <c r="B40" s="16">
+        <v>270</v>
+      </c>
+      <c r="C40" s="16">
+        <v>0</v>
+      </c>
+      <c r="D40" s="16">
+        <v>15</v>
+      </c>
+      <c r="E40" s="16">
+        <v>10</v>
+      </c>
+      <c r="F40" s="16">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="13">
+        <v>2069</v>
+      </c>
+      <c r="B41" s="9">
+        <v>275</v>
+      </c>
+      <c r="C41" s="16">
+        <v>0</v>
+      </c>
+      <c r="D41" s="16">
+        <v>15</v>
+      </c>
+      <c r="E41" s="16">
+        <v>15</v>
+      </c>
+      <c r="F41" s="16">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="15">
+        <v>2070</v>
+      </c>
+      <c r="B42" s="9">
+        <v>280</v>
+      </c>
+      <c r="C42" s="16">
+        <v>0</v>
+      </c>
+      <c r="D42" s="16">
+        <v>15</v>
+      </c>
+      <c r="E42" s="16">
+        <v>15</v>
+      </c>
+      <c r="F42" s="16">
+        <v>0</v>
+      </c>
+      <c r="G42" s="17">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="13">
+        <v>2071</v>
+      </c>
+      <c r="B43" s="16">
+        <v>285</v>
+      </c>
+      <c r="C43" s="16">
+        <v>0</v>
+      </c>
+      <c r="D43" s="16">
+        <v>15</v>
+      </c>
+      <c r="E43" s="16">
+        <v>15</v>
+      </c>
+      <c r="F43" s="16">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="13">
+        <v>2072</v>
+      </c>
+      <c r="B44" s="9">
+        <v>290</v>
+      </c>
+      <c r="C44" s="16">
+        <v>0</v>
+      </c>
+      <c r="D44" s="16">
+        <v>15</v>
+      </c>
+      <c r="E44" s="16">
+        <v>15</v>
+      </c>
+      <c r="F44" s="16">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="13">
+        <v>2073</v>
+      </c>
+      <c r="B45" s="9">
+        <v>295</v>
+      </c>
+      <c r="C45" s="16">
+        <v>0</v>
+      </c>
+      <c r="D45" s="16">
+        <v>15</v>
+      </c>
+      <c r="E45" s="16">
+        <v>15</v>
+      </c>
+      <c r="F45" s="16">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="15">
+        <v>2074</v>
+      </c>
+      <c r="B46" s="16">
+        <v>300</v>
+      </c>
+      <c r="C46" s="16">
+        <v>0</v>
+      </c>
+      <c r="D46" s="16">
+        <v>15</v>
+      </c>
+      <c r="E46" s="16">
+        <v>15</v>
+      </c>
+      <c r="F46" s="16">
+        <v>0</v>
+      </c>
+      <c r="G46" s="17">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="13">
+        <v>2075</v>
+      </c>
+      <c r="B47" s="9">
+        <v>305</v>
+      </c>
+      <c r="C47" s="16">
+        <v>0</v>
+      </c>
+      <c r="D47" s="16">
+        <v>15</v>
+      </c>
+      <c r="E47" s="16">
+        <v>15</v>
+      </c>
+      <c r="F47" s="16">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="13">
+        <v>2076</v>
+      </c>
+      <c r="B48" s="9">
+        <v>310</v>
+      </c>
+      <c r="C48" s="16">
+        <v>0</v>
+      </c>
+      <c r="D48" s="16">
+        <v>15</v>
+      </c>
+      <c r="E48" s="16">
+        <v>15</v>
+      </c>
+      <c r="F48" s="16">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="13">
+        <v>2077</v>
+      </c>
+      <c r="B49" s="16">
+        <v>315</v>
+      </c>
+      <c r="C49" s="16">
+        <v>0</v>
+      </c>
+      <c r="D49" s="16">
+        <v>10</v>
+      </c>
+      <c r="E49" s="16">
+        <v>10</v>
+      </c>
+      <c r="F49" s="16">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="15">
+        <v>2078</v>
+      </c>
+      <c r="B50" s="9">
+        <v>320</v>
+      </c>
+      <c r="C50" s="16">
+        <v>0</v>
+      </c>
+      <c r="D50" s="16">
+        <v>15</v>
+      </c>
+      <c r="E50" s="16">
+        <v>15</v>
+      </c>
+      <c r="F50" s="16">
+        <v>0</v>
+      </c>
+      <c r="G50" s="17">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="13">
+        <v>2079</v>
+      </c>
+      <c r="B51" s="9">
+        <v>325</v>
+      </c>
+      <c r="C51" s="16">
+        <v>0</v>
+      </c>
+      <c r="D51" s="16">
+        <v>15</v>
+      </c>
+      <c r="E51" s="16">
+        <v>15</v>
+      </c>
+      <c r="F51" s="16">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="13">
+        <v>2080</v>
+      </c>
+      <c r="B52" s="16">
+        <v>330</v>
+      </c>
+      <c r="C52" s="16">
+        <v>0</v>
+      </c>
+      <c r="D52" s="16">
+        <v>15</v>
+      </c>
+      <c r="E52" s="16">
+        <v>15</v>
+      </c>
+      <c r="F52" s="16">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="13">
+        <v>2081</v>
+      </c>
+      <c r="B53" s="9">
+        <v>335</v>
+      </c>
+      <c r="C53" s="16">
+        <v>0</v>
+      </c>
+      <c r="D53" s="16">
+        <v>15</v>
+      </c>
+      <c r="E53" s="16">
+        <v>15</v>
+      </c>
+      <c r="F53" s="16">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="15">
+        <v>2082</v>
+      </c>
+      <c r="B54" s="9">
+        <v>340</v>
+      </c>
+      <c r="C54" s="16">
+        <v>0</v>
+      </c>
+      <c r="D54" s="16">
+        <v>15</v>
+      </c>
+      <c r="E54" s="16">
+        <v>15</v>
+      </c>
+      <c r="F54" s="16">
+        <v>0</v>
+      </c>
+      <c r="G54" s="17">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="13">
+        <v>2083</v>
+      </c>
+      <c r="B55" s="16">
+        <v>345</v>
+      </c>
+      <c r="C55" s="16">
+        <v>0</v>
+      </c>
+      <c r="D55" s="16">
+        <v>15</v>
+      </c>
+      <c r="E55" s="16">
+        <v>15</v>
+      </c>
+      <c r="F55" s="16">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="13">
+        <v>2084</v>
+      </c>
+      <c r="B56" s="9">
+        <v>350</v>
+      </c>
+      <c r="C56" s="16">
+        <v>0</v>
+      </c>
+      <c r="D56" s="16">
+        <v>15</v>
+      </c>
+      <c r="E56" s="16">
+        <v>15</v>
+      </c>
+      <c r="F56" s="16">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="13">
+        <v>2085</v>
+      </c>
+      <c r="B57" s="9">
+        <v>355</v>
+      </c>
+      <c r="C57" s="16">
+        <v>0</v>
+      </c>
+      <c r="D57" s="16">
+        <v>15</v>
+      </c>
+      <c r="E57" s="16">
+        <v>15</v>
+      </c>
+      <c r="F57" s="16">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="15">
+        <v>2086</v>
+      </c>
+      <c r="B58" s="16">
+        <v>360</v>
+      </c>
+      <c r="C58" s="16">
+        <v>0</v>
+      </c>
+      <c r="D58" s="16">
+        <v>15</v>
+      </c>
+      <c r="E58" s="16">
+        <v>15</v>
+      </c>
+      <c r="F58" s="16">
+        <v>0</v>
+      </c>
+      <c r="G58" s="17">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="13">
+        <v>2087</v>
+      </c>
+      <c r="B59" s="9">
+        <v>365</v>
+      </c>
+      <c r="C59" s="16">
+        <v>0</v>
+      </c>
+      <c r="D59" s="16">
+        <v>10</v>
+      </c>
+      <c r="E59" s="16">
+        <v>15</v>
+      </c>
+      <c r="F59" s="16">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="13">
+        <v>2088</v>
+      </c>
+      <c r="B60" s="9">
+        <v>370</v>
+      </c>
+      <c r="C60" s="16">
+        <v>0</v>
+      </c>
+      <c r="D60" s="16">
+        <v>15</v>
+      </c>
+      <c r="E60" s="16">
+        <v>15</v>
+      </c>
+      <c r="F60" s="16">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="13">
+        <v>2089</v>
+      </c>
+      <c r="B61" s="16">
+        <v>375</v>
+      </c>
+      <c r="C61" s="16">
+        <v>0</v>
+      </c>
+      <c r="D61" s="16">
+        <v>15</v>
+      </c>
+      <c r="E61" s="16">
+        <v>10</v>
+      </c>
+      <c r="F61" s="16">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="15">
+        <v>2090</v>
+      </c>
+      <c r="B62" s="9">
+        <v>380</v>
+      </c>
+      <c r="C62" s="16">
+        <v>0</v>
+      </c>
+      <c r="D62" s="16">
+        <v>15</v>
+      </c>
+      <c r="E62" s="16">
+        <v>15</v>
+      </c>
+      <c r="F62" s="16">
+        <v>0</v>
+      </c>
+      <c r="G62" s="17">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="13">
+        <v>2091</v>
+      </c>
+      <c r="B63" s="9">
+        <v>385</v>
+      </c>
+      <c r="C63" s="16">
+        <v>0</v>
+      </c>
+      <c r="D63" s="16">
+        <v>15</v>
+      </c>
+      <c r="E63" s="16">
+        <v>15</v>
+      </c>
+      <c r="F63" s="16">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="13">
+        <v>2092</v>
+      </c>
+      <c r="B64" s="16">
+        <v>390</v>
+      </c>
+      <c r="C64" s="16">
+        <v>0</v>
+      </c>
+      <c r="D64" s="16">
+        <v>15</v>
+      </c>
+      <c r="E64" s="16">
+        <v>15</v>
+      </c>
+      <c r="F64" s="16">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="13">
+        <v>2093</v>
+      </c>
+      <c r="B65" s="9">
+        <v>395</v>
+      </c>
+      <c r="C65" s="16">
+        <v>0</v>
+      </c>
+      <c r="D65" s="16">
+        <v>15</v>
+      </c>
+      <c r="E65" s="16">
+        <v>10</v>
+      </c>
+      <c r="F65" s="16">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="15">
+        <v>2094</v>
+      </c>
+      <c r="B66" s="9">
+        <v>400</v>
+      </c>
+      <c r="C66" s="16">
+        <v>0</v>
+      </c>
+      <c r="D66" s="16">
+        <v>10</v>
+      </c>
+      <c r="E66" s="16">
+        <v>15</v>
+      </c>
+      <c r="F66" s="16">
+        <v>0</v>
+      </c>
+      <c r="G66" s="17">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="13">
+        <v>2095</v>
+      </c>
+      <c r="B67" s="16">
+        <v>405</v>
+      </c>
+      <c r="C67" s="16">
+        <v>0</v>
+      </c>
+      <c r="D67" s="16">
+        <v>15</v>
+      </c>
+      <c r="E67" s="16">
+        <v>15</v>
+      </c>
+      <c r="F67" s="16">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="13">
+        <v>2096</v>
+      </c>
+      <c r="B68" s="9">
+        <v>410</v>
+      </c>
+      <c r="C68" s="16">
+        <v>0</v>
+      </c>
+      <c r="D68" s="16">
+        <v>15</v>
+      </c>
+      <c r="E68" s="16">
+        <v>15</v>
+      </c>
+      <c r="F68" s="16">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="13">
+        <v>2097</v>
+      </c>
+      <c r="B69" s="9">
+        <v>415</v>
+      </c>
+      <c r="C69" s="16">
+        <v>0</v>
+      </c>
+      <c r="D69" s="16">
+        <v>15</v>
+      </c>
+      <c r="E69" s="16">
+        <v>15</v>
+      </c>
+      <c r="F69" s="16">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="15">
+        <v>2098</v>
+      </c>
+      <c r="B70" s="16">
+        <v>420</v>
+      </c>
+      <c r="C70" s="16">
+        <v>0</v>
+      </c>
+      <c r="D70" s="16">
+        <v>15</v>
+      </c>
+      <c r="E70" s="16">
+        <v>10</v>
+      </c>
+      <c r="F70" s="16">
+        <v>0</v>
+      </c>
+      <c r="G70" s="17">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="13">
+        <v>2099</v>
+      </c>
+      <c r="B71" s="9">
+        <v>425</v>
+      </c>
+      <c r="C71" s="16">
+        <v>0</v>
+      </c>
+      <c r="D71" s="16">
+        <v>15</v>
+      </c>
+      <c r="E71" s="16">
+        <v>15</v>
+      </c>
+      <c r="F71" s="16">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="13">
+        <v>2100</v>
+      </c>
+      <c r="B72" s="9">
+        <v>430</v>
+      </c>
+      <c r="C72" s="16">
+        <v>0</v>
+      </c>
+      <c r="D72" s="16">
+        <v>15</v>
+      </c>
+      <c r="E72" s="16">
+        <v>15</v>
+      </c>
+      <c r="F72" s="16">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
